--- a/public/files/PT Rukun Raharja Tbk (RAJA)/(Revision)_RAJA_Income_Statement.xlsx
+++ b/public/files/PT Rukun Raharja Tbk (RAJA)/(Revision)_RAJA_Income_Statement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/melvinjusuf/Downloads/portfolio-project/public/files/PT Rukun Raharja Tbk (RAJA)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D810FEFD-3D77-4949-92D7-E65C2D15F355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33037E9A-656C-A14D-971F-56A14F1781CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -143,9 +143,6 @@
     <t xml:space="preserve">    Laba (Rugi) Selisih Kurs</t>
   </si>
   <si>
-    <t>INCOME STATEMENT - RAJA</t>
-  </si>
-  <si>
     <t xml:space="preserve">    Adjustment</t>
   </si>
   <si>
@@ -171,16 +168,17 @@
   </si>
   <si>
     <t>Key Ratio</t>
+  </si>
+  <si>
+    <t>INCOME STATEMENT - PT Rukun Raharja Tbk (RAJA)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
-    <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-m"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\);\-m"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0&quot; B&quot;;\(#,##0\)&quot; B&quot;;\-"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -355,26 +353,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -650,32 +647,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
+      <c r="A1" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -716,31 +713,31 @@
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="9">
         <v>2487</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="9">
         <v>1993</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="9">
         <v>1683</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="9">
         <v>1728</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="9">
         <v>1440</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="9">
         <v>1405</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="9">
         <v>1885</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="9">
         <v>3108</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="9">
         <v>4033</v>
       </c>
       <c r="K5" s="9">
@@ -751,78 +748,78 @@
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="9">
         <v>-2165</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="9">
         <v>-1665</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="9">
         <v>-1391</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="9">
         <v>-1486</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="9">
         <v>-1205</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="9">
         <v>-1184</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="9">
         <v>-1512</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="9">
         <v>-2102</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="9">
         <v>-2936</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="9">
         <v>-3205</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="10">
         <f t="shared" ref="B7:K7" si="0">B5+B6</f>
         <v>322</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="10">
         <f t="shared" si="0"/>
         <v>328</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="10">
         <f t="shared" si="0"/>
         <v>292</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="10">
         <f t="shared" si="0"/>
         <v>242</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="10">
         <f t="shared" si="0"/>
         <v>235</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="10">
         <f t="shared" si="0"/>
         <v>221</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="10">
         <f t="shared" si="0"/>
         <v>373</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="10">
         <f t="shared" si="0"/>
         <v>1006</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="10">
         <f t="shared" si="0"/>
         <v>1097</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="10">
         <f t="shared" si="0"/>
         <v>1189</v>
       </c>
@@ -831,157 +828,176 @@
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="9">
         <v>-168</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="9">
         <v>-302</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="9">
         <v>-204</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="9">
         <v>-202</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="9">
         <v>-152</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="9">
         <v>-155</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="9">
         <v>-189</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="9">
         <v>-273</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="9">
         <v>-315</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="9">
         <v>-417</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="11">
         <f t="shared" ref="B9:K9" si="1">B7+B8</f>
         <v>154</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="10">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="10">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="10">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="10">
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="10">
         <f t="shared" si="1"/>
         <v>66</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="10">
         <f t="shared" si="1"/>
         <v>184</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="10">
         <f t="shared" si="1"/>
         <v>733</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="10">
         <f t="shared" si="1"/>
         <v>782</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="10">
         <f t="shared" si="1"/>
         <v>772</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B10" s="12"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="5" t="s">
         <v>16</v>
       </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="14">
         <v>-2</v>
       </c>
-      <c r="C12" s="13">
-        <v>0</v>
-      </c>
-      <c r="D12" s="13">
-        <v>0</v>
-      </c>
-      <c r="E12" s="13">
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <v>0</v>
+      </c>
+      <c r="E12" s="14">
         <v>15</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="14">
         <v>-7</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="14">
         <v>1</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="14">
         <v>-31</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="14">
         <v>5</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="14">
         <v>-5</v>
       </c>
-      <c r="K12" s="13">
+      <c r="K12" s="14">
         <v>-37</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="11">
-        <v>0</v>
-      </c>
-      <c r="C13" s="11">
-        <v>0</v>
-      </c>
-      <c r="D13" s="13">
-        <v>0</v>
-      </c>
-      <c r="E13" s="11">
-        <v>0</v>
-      </c>
-      <c r="F13" s="11">
-        <v>0</v>
-      </c>
-      <c r="G13" s="11">
-        <v>0</v>
-      </c>
-      <c r="H13" s="11">
-        <v>0</v>
-      </c>
-      <c r="I13" s="11">
-        <v>0</v>
-      </c>
-      <c r="J13" s="11">
-        <v>0</v>
-      </c>
-      <c r="K13" s="11">
+      <c r="B13" s="15">
+        <v>0</v>
+      </c>
+      <c r="C13" s="15">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>0</v>
+      </c>
+      <c r="E13" s="15">
+        <v>0</v>
+      </c>
+      <c r="F13" s="15">
+        <v>0</v>
+      </c>
+      <c r="G13" s="15">
+        <v>0</v>
+      </c>
+      <c r="H13" s="15">
+        <v>0</v>
+      </c>
+      <c r="I13" s="15">
+        <v>0</v>
+      </c>
+      <c r="J13" s="15">
+        <v>0</v>
+      </c>
+      <c r="K13" s="15">
         <v>0</v>
       </c>
     </row>
@@ -989,34 +1005,34 @@
       <c r="A14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="15">
         <v>-52</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="15">
         <v>-74</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="14">
         <v>-94</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="15">
         <v>-47</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="15">
         <v>-44</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="15">
         <v>-35</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="15">
         <v>-40</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="15">
         <v>-141</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="15">
         <v>-164</v>
       </c>
-      <c r="K14" s="11">
+      <c r="K14" s="15">
         <v>-166</v>
       </c>
     </row>
@@ -1024,228 +1040,228 @@
       <c r="A15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="4">
-        <v>0</v>
-      </c>
-      <c r="C15" s="4">
-        <v>0</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="4">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4">
+      <c r="B15" s="9">
+        <v>0</v>
+      </c>
+      <c r="C15" s="9">
+        <v>0</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9">
+        <v>0</v>
+      </c>
+      <c r="G15" s="9">
         <v>44</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="9">
         <v>104</v>
       </c>
-      <c r="I15" s="4">
+      <c r="I15" s="9">
         <v>114</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15" s="9">
         <v>98</v>
       </c>
-      <c r="K15" s="4">
+      <c r="K15" s="9">
         <v>325</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="4">
-        <v>0</v>
-      </c>
-      <c r="C16" s="4">
+      <c r="A16" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="9">
+        <v>0</v>
+      </c>
+      <c r="C16" s="9">
         <v>301</v>
       </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4">
-        <v>0</v>
-      </c>
-      <c r="H16" s="4">
-        <v>0</v>
-      </c>
-      <c r="I16" s="4">
-        <v>0</v>
-      </c>
-      <c r="J16" s="4">
-        <v>0</v>
-      </c>
-      <c r="K16" s="4">
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="9">
+        <v>0</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9">
+        <v>0</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0</v>
+      </c>
+      <c r="F17" s="9">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0</v>
+      </c>
+      <c r="H17" s="9">
+        <v>0</v>
+      </c>
+      <c r="I17" s="9">
+        <v>0</v>
+      </c>
+      <c r="J17" s="9">
+        <v>0</v>
+      </c>
+      <c r="K17" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="4">
-        <v>0</v>
-      </c>
-      <c r="C17" s="4">
-        <v>0</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="4">
-        <v>0</v>
-      </c>
-      <c r="F17" s="4">
-        <v>0</v>
-      </c>
-      <c r="G17" s="4">
-        <v>0</v>
-      </c>
-      <c r="H17" s="4">
-        <v>0</v>
-      </c>
-      <c r="I17" s="4">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4">
-        <v>0</v>
-      </c>
-      <c r="K17" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="4">
+      <c r="B18" s="9">
         <v>44</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="9">
         <v>-8</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="9">
         <v>220</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="9">
         <v>120</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="9">
         <v>34</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="9">
         <v>-9</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18" s="9">
         <v>-22</v>
       </c>
-      <c r="I18" s="4">
+      <c r="I18" s="9">
         <v>-90</v>
       </c>
-      <c r="J18" s="4">
+      <c r="J18" s="9">
         <v>-11</v>
       </c>
-      <c r="K18" s="4">
+      <c r="K18" s="9">
         <v>-78</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="10">
         <f t="shared" ref="B19:J19" si="2">SUM(B12:B18)</f>
         <v>-10</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="10">
         <f t="shared" si="2"/>
         <v>219</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="10">
         <f t="shared" si="2"/>
         <v>126</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="10">
         <f t="shared" si="2"/>
         <v>88</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="10">
         <f t="shared" si="2"/>
         <v>-17</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="10">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="10">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="10">
         <f t="shared" si="2"/>
         <v>-112</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19" s="10">
         <f t="shared" si="2"/>
         <v>-82</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="10">
         <f>SUM(K12:K18)</f>
         <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="10">
         <f t="shared" ref="B20" si="3">B9+B19</f>
         <v>144</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="10">
         <f t="shared" ref="C20" si="4">C9+C19</f>
         <v>245</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="10">
         <f t="shared" ref="D20" si="5">D9+D19</f>
         <v>214</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="10">
         <f t="shared" ref="E20" si="6">E9+E19</f>
         <v>128</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="10">
         <f t="shared" ref="F20" si="7">F9+F19</f>
         <v>66</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="10">
         <f t="shared" ref="G20" si="8">G9+G19</f>
         <v>67</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="10">
         <f t="shared" ref="H20" si="9">H9+H19</f>
         <v>195</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="10">
         <f t="shared" ref="I20" si="10">I9+I19</f>
         <v>621</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="10">
         <f t="shared" ref="J20" si="11">J9+J19</f>
         <v>700</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="10">
         <f t="shared" ref="K20" si="12">K9+K19</f>
         <v>816</v>
       </c>
@@ -1254,34 +1270,34 @@
       <c r="A21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="9">
         <v>-42</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="9">
         <v>-60</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="9">
         <v>-38</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="9">
         <v>-38</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="9">
         <v>-29</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="9">
         <v>-18</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="9">
         <v>-32</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I21" s="9">
         <v>-206</v>
       </c>
-      <c r="J21" s="4">
+      <c r="J21" s="9">
         <v>-240</v>
       </c>
-      <c r="K21" s="4">
+      <c r="K21" s="9">
         <v>-239</v>
       </c>
     </row>
@@ -1289,148 +1305,148 @@
       <c r="A22" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="9">
         <v>103</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="9">
         <v>185</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="9">
         <v>177</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="9">
         <v>90</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="9">
         <v>37</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G22" s="9">
         <v>49</v>
       </c>
-      <c r="H22" s="4">
+      <c r="H22" s="9">
         <v>161</v>
       </c>
-      <c r="I22" s="4">
+      <c r="I22" s="9">
         <v>414</v>
       </c>
-      <c r="J22" s="4">
+      <c r="J22" s="9">
         <v>461</v>
       </c>
-      <c r="K22" s="4">
+      <c r="K22" s="9">
         <v>577</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="9">
+        <v>0</v>
+      </c>
+      <c r="C23" s="9">
+        <v>0</v>
+      </c>
+      <c r="D23" s="9">
+        <v>0</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0</v>
+      </c>
+      <c r="F23" s="9">
+        <v>0</v>
+      </c>
+      <c r="G23" s="9">
+        <v>0</v>
+      </c>
+      <c r="H23" s="9">
+        <v>0</v>
+      </c>
+      <c r="I23" s="9">
+        <v>0</v>
+      </c>
+      <c r="J23" s="9">
+        <v>0</v>
+      </c>
+      <c r="K23" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="4">
-        <v>0</v>
-      </c>
-      <c r="C23" s="4">
-        <v>0</v>
-      </c>
-      <c r="D23" s="4">
-        <v>0</v>
-      </c>
-      <c r="E23" s="4">
-        <v>0</v>
-      </c>
-      <c r="F23" s="4">
-        <v>0</v>
-      </c>
-      <c r="G23" s="4">
-        <v>0</v>
-      </c>
-      <c r="H23" s="4">
-        <v>0</v>
-      </c>
-      <c r="I23" s="4">
-        <v>0</v>
-      </c>
-      <c r="J23" s="4">
-        <v>0</v>
-      </c>
-      <c r="K23" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="4">
-        <v>0</v>
-      </c>
-      <c r="C24" s="4">
-        <v>0</v>
-      </c>
-      <c r="D24" s="4">
-        <v>0</v>
-      </c>
-      <c r="E24" s="4">
-        <v>0</v>
-      </c>
-      <c r="F24" s="4">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4">
-        <v>0</v>
-      </c>
-      <c r="H24" s="4">
-        <v>0</v>
-      </c>
-      <c r="I24" s="4">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4">
-        <v>0</v>
-      </c>
-      <c r="K24" s="4">
+      <c r="B24" s="9">
+        <v>0</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0</v>
+      </c>
+      <c r="D24" s="9">
+        <v>0</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0</v>
+      </c>
+      <c r="F24" s="9">
+        <v>0</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9">
+        <v>0</v>
+      </c>
+      <c r="I24" s="9">
+        <v>0</v>
+      </c>
+      <c r="J24" s="9">
+        <v>0</v>
+      </c>
+      <c r="K24" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="10">
         <f t="shared" ref="B25" si="13">B22+B24</f>
         <v>103</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="10">
         <f t="shared" ref="C25" si="14">C22+C24</f>
         <v>185</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="10">
         <f t="shared" ref="D25" si="15">D22+D24</f>
         <v>177</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="10">
         <f t="shared" ref="E25" si="16">E22+E24</f>
         <v>90</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="10">
         <f t="shared" ref="F25" si="17">F22+F24</f>
         <v>37</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="10">
         <f t="shared" ref="G25" si="18">G22+G24</f>
         <v>49</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="10">
         <f t="shared" ref="H25" si="19">H22+H24</f>
         <v>161</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="10">
         <f t="shared" ref="I25" si="20">I22+I24</f>
         <v>414</v>
       </c>
-      <c r="J25" s="6">
+      <c r="J25" s="10">
         <f t="shared" ref="J25" si="21">J22+J24</f>
         <v>461</v>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="10">
         <f t="shared" ref="K25" si="22">K22+K24</f>
         <v>577</v>
       </c>
@@ -1439,119 +1455,141 @@
       <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="9">
         <v>3</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="9">
         <v>8</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="9">
         <v>2</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="9">
         <v>-2</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="9">
         <v>-1</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G26" s="9">
         <v>2</v>
       </c>
-      <c r="H26" s="4">
-        <v>0</v>
-      </c>
-      <c r="I26" s="4">
+      <c r="H26" s="9">
+        <v>0</v>
+      </c>
+      <c r="I26" s="9">
         <v>-2</v>
       </c>
-      <c r="J26" s="4">
-        <v>0</v>
-      </c>
-      <c r="K26" s="4">
+      <c r="J26" s="9">
+        <v>0</v>
+      </c>
+      <c r="K26" s="9">
         <v>-23</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="10">
         <f t="shared" ref="B27" si="23">B25+B26</f>
         <v>106</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="10">
         <f t="shared" ref="C27" si="24">C25+C26</f>
         <v>193</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="10">
         <f t="shared" ref="D27" si="25">D25+D26</f>
         <v>179</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="10">
         <f t="shared" ref="E27" si="26">E25+E26</f>
         <v>88</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="10">
         <f t="shared" ref="F27" si="27">F25+F26</f>
         <v>36</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="10">
         <f t="shared" ref="G27" si="28">G25+G26</f>
         <v>51</v>
       </c>
-      <c r="H27" s="6">
+      <c r="H27" s="10">
         <f t="shared" ref="H27" si="29">H25+H26</f>
         <v>161</v>
       </c>
-      <c r="I27" s="6">
+      <c r="I27" s="10">
         <f t="shared" ref="I27" si="30">I25+I26</f>
         <v>412</v>
       </c>
-      <c r="J27" s="6">
+      <c r="J27" s="10">
         <f t="shared" ref="J27" si="31">J25+J26</f>
         <v>461</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="10">
         <f t="shared" ref="K27" si="32">K25+K26</f>
         <v>554</v>
       </c>
     </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+    </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="9">
         <v>87</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="9">
         <v>156</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="9">
         <v>163</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="9">
         <v>81</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="9">
         <v>20</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G30" s="9">
         <v>32</v>
       </c>
-      <c r="H30" s="4">
+      <c r="H30" s="9">
         <v>131</v>
       </c>
-      <c r="I30" s="4">
+      <c r="I30" s="9">
         <v>391</v>
       </c>
-      <c r="J30" s="4">
+      <c r="J30" s="9">
         <v>405</v>
       </c>
-      <c r="K30" s="4">
+      <c r="K30" s="9">
         <v>449</v>
       </c>
     </row>
@@ -1559,154 +1597,176 @@
       <c r="A31" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="9">
         <v>16</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="9">
         <v>29</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="9">
         <v>14</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="9">
         <v>9</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="9">
         <v>17</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G31" s="9">
         <v>16</v>
       </c>
-      <c r="H31" s="4">
+      <c r="H31" s="9">
         <v>30</v>
       </c>
-      <c r="I31" s="4">
+      <c r="I31" s="9">
         <v>24</v>
       </c>
-      <c r="J31" s="4">
+      <c r="J31" s="9">
         <v>56</v>
       </c>
-      <c r="K31" s="4">
+      <c r="K31" s="9">
         <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="4" t="s">
+      <c r="A32" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H32" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="I32" s="4" t="s">
+      <c r="I32" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="J32" s="4" t="s">
+      <c r="J32" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K32" s="4" t="s">
+      <c r="K32" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="10">
         <f t="shared" ref="B33" si="33">SUM(B30:B32)</f>
         <v>103</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="10">
         <f t="shared" ref="C33" si="34">SUM(C30:C32)</f>
         <v>185</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="10">
         <f t="shared" ref="D33" si="35">SUM(D30:D32)</f>
         <v>177</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="10">
         <f t="shared" ref="E33" si="36">SUM(E30:E32)</f>
         <v>90</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="10">
         <f t="shared" ref="F33" si="37">SUM(F30:F32)</f>
         <v>37</v>
       </c>
-      <c r="G33" s="6">
+      <c r="G33" s="10">
         <f t="shared" ref="G33" si="38">SUM(G30:G32)</f>
         <v>48</v>
       </c>
-      <c r="H33" s="6">
+      <c r="H33" s="10">
         <f t="shared" ref="H33" si="39">SUM(H30:H32)</f>
         <v>161</v>
       </c>
-      <c r="I33" s="6">
+      <c r="I33" s="10">
         <f t="shared" ref="I33" si="40">SUM(I30:I32)</f>
         <v>415</v>
       </c>
-      <c r="J33" s="6">
+      <c r="J33" s="10">
         <f t="shared" ref="J33" si="41">SUM(J30:J32)</f>
         <v>461</v>
       </c>
-      <c r="K33" s="6">
+      <c r="K33" s="10">
         <f t="shared" ref="K33" si="42">SUM(K30:K32)</f>
         <v>577</v>
       </c>
     </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+    </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="5" t="s">
         <v>31</v>
       </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="9">
         <v>89</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="9">
         <v>161</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="9">
         <v>165</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36" s="9">
         <v>79</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="9">
         <v>19</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G36" s="9">
         <v>34</v>
       </c>
-      <c r="H36" s="4">
+      <c r="H36" s="9">
         <v>132</v>
       </c>
-      <c r="I36" s="4">
+      <c r="I36" s="9">
         <v>389</v>
       </c>
-      <c r="J36" s="4">
+      <c r="J36" s="9">
         <v>405</v>
       </c>
-      <c r="K36" s="4">
+      <c r="K36" s="9">
         <v>427</v>
       </c>
     </row>
@@ -1714,182 +1774,182 @@
       <c r="A37" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="9">
         <v>17</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="9">
         <v>31</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="9">
         <v>15</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E37" s="9">
         <v>9</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F37" s="9">
         <v>16</v>
       </c>
-      <c r="G37" s="4">
+      <c r="G37" s="9">
         <v>17</v>
       </c>
-      <c r="H37" s="4">
+      <c r="H37" s="9">
         <v>30</v>
       </c>
-      <c r="I37" s="4">
+      <c r="I37" s="9">
         <v>23</v>
       </c>
-      <c r="J37" s="4">
+      <c r="J37" s="9">
         <v>56</v>
       </c>
-      <c r="K37" s="4">
+      <c r="K37" s="9">
         <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="6">
+      <c r="B38" s="10">
         <f t="shared" ref="B38" si="43">SUM(B36:B37)</f>
         <v>106</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="10">
         <f t="shared" ref="C38" si="44">SUM(C36:C37)</f>
         <v>192</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="10">
         <f t="shared" ref="D38" si="45">SUM(D36:D37)</f>
         <v>180</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="10">
         <f t="shared" ref="E38" si="46">SUM(E36:E37)</f>
         <v>88</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38" s="10">
         <f t="shared" ref="F38" si="47">SUM(F36:F37)</f>
         <v>35</v>
       </c>
-      <c r="G38" s="6">
+      <c r="G38" s="10">
         <f t="shared" ref="G38" si="48">SUM(G36:G37)</f>
         <v>51</v>
       </c>
-      <c r="H38" s="6">
+      <c r="H38" s="10">
         <f t="shared" ref="H38" si="49">SUM(H36:H37)</f>
         <v>162</v>
       </c>
-      <c r="I38" s="6">
+      <c r="I38" s="10">
         <f t="shared" ref="I38" si="50">SUM(I36:I37)</f>
         <v>412</v>
       </c>
-      <c r="J38" s="6">
+      <c r="J38" s="10">
         <f t="shared" ref="J38" si="51">SUM(J36:J37)</f>
         <v>461</v>
       </c>
-      <c r="K38" s="6">
+      <c r="K38" s="10">
         <f t="shared" ref="K38" si="52">SUM(K36:K37)</f>
         <v>554</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A41" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
+      <c r="A41" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="9">
+        <v>4.08</v>
+      </c>
+      <c r="C42" s="9">
+        <v>4.08</v>
+      </c>
+      <c r="D42" s="9">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="E42" s="9">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="F42" s="9">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="G42" s="9">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="H42" s="9">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="I42" s="9">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="J42" s="9">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="K42" s="9">
+        <v>4.2300000000000004</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="14">
-        <v>4.08</v>
-      </c>
-      <c r="C42" s="14">
-        <v>4.08</v>
-      </c>
-      <c r="D42" s="14">
-        <v>4.2300000000000004</v>
-      </c>
-      <c r="E42" s="14">
-        <v>4.2300000000000004</v>
-      </c>
-      <c r="F42" s="14">
-        <v>4.2300000000000004</v>
-      </c>
-      <c r="G42" s="14">
-        <v>4.2300000000000004</v>
-      </c>
-      <c r="H42" s="14">
-        <v>4.2300000000000004</v>
-      </c>
-      <c r="I42" s="14">
-        <v>4.2300000000000004</v>
-      </c>
-      <c r="J42" s="14">
-        <v>4.2300000000000004</v>
-      </c>
-      <c r="K42" s="14">
-        <v>4.2300000000000004</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A43" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="15">
+      <c r="B43" s="8">
         <f t="shared" ref="B43:J43" si="53">B30/B42</f>
         <v>21.323529411764707</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="8">
         <f t="shared" si="53"/>
         <v>38.235294117647058</v>
       </c>
-      <c r="D43" s="15">
+      <c r="D43" s="8">
         <f t="shared" si="53"/>
         <v>38.534278959810869</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="8">
         <f t="shared" si="53"/>
         <v>19.148936170212764</v>
       </c>
-      <c r="F43" s="15">
+      <c r="F43" s="8">
         <f t="shared" si="53"/>
         <v>4.7281323877068555</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="8">
         <f t="shared" si="53"/>
         <v>7.5650118203309686</v>
       </c>
-      <c r="H43" s="15">
+      <c r="H43" s="8">
         <f t="shared" si="53"/>
         <v>30.969267139479904</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="8">
         <f t="shared" si="53"/>
         <v>92.43498817966902</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="8">
         <f t="shared" si="53"/>
         <v>95.744680851063819</v>
       </c>
-      <c r="K43" s="15">
+      <c r="K43" s="8">
         <f>K30/K42</f>
         <v>106.1465721040189</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" s="8"/>
+      <c r="A44" s="6"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A45" s="8"/>
+      <c r="A45" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
